--- a/data/trans_orig/P21_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176998</t>
+          <t>174802</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225931</t>
+          <t>224358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>312108</t>
+          <t>312365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>371720</t>
+          <t>377621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>500612</t>
+          <t>500576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>581049</t>
+          <t>581056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>805792</t>
+          <t>807365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>854725</t>
+          <t>856921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>943393</t>
+          <t>937492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1003005</t>
+          <t>1002748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1765786</t>
+          <t>1765779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1846223</t>
+          <t>1846259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251656</t>
+          <t>253785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>312947</t>
+          <t>312891</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>345914</t>
+          <t>345939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>413788</t>
+          <t>409083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>611147</t>
+          <t>615404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>707704</t>
+          <t>704252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1379581</t>
+          <t>1379637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1440872</t>
+          <t>1438743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1172945</t>
+          <t>1177650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1240819</t>
+          <t>1240794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2571556</t>
+          <t>2575008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2668113</t>
+          <t>2663856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64144</t>
+          <t>63440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99105</t>
+          <t>99624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87957</t>
+          <t>88194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124766</t>
+          <t>124769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160563</t>
+          <t>159712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214475</t>
+          <t>209597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452303</t>
+          <t>451784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487264</t>
+          <t>487968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>351646</t>
+          <t>351643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>388455</t>
+          <t>388218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>813345</t>
+          <t>818223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>867257</t>
+          <t>868108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>521268</t>
+          <t>515224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>607385</t>
+          <t>602739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>774989</t>
+          <t>774864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>873724</t>
+          <t>872861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1317955</t>
+          <t>1319432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1449133</t>
+          <t>1450792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2668274</t>
+          <t>2672920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2754391</t>
+          <t>2760435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2504533</t>
+          <t>2505396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2603268</t>
+          <t>2603393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5204782</t>
+          <t>5203123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5335960</t>
+          <t>5334483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225578</t>
+          <t>225645</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280572</t>
+          <t>278109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>374398</t>
+          <t>377691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444998</t>
+          <t>444573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616095</t>
+          <t>616352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>706207</t>
+          <t>706495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>693344</t>
+          <t>695807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748338</t>
+          <t>748271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>891840</t>
+          <t>892265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>962440</t>
+          <t>959147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1604547</t>
+          <t>1604259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1694659</t>
+          <t>1694402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>351337</t>
+          <t>348086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424952</t>
+          <t>424969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>415672</t>
+          <t>413502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>488003</t>
+          <t>490932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>787733</t>
+          <t>785830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>894640</t>
+          <t>889402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1537051</t>
+          <t>1537034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1610666</t>
+          <t>1613917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1267653</t>
+          <t>1264724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1339984</t>
+          <t>1342154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2823019</t>
+          <t>2828257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2929926</t>
+          <t>2931829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86450</t>
+          <t>86169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97217</t>
+          <t>97376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134785</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157830</t>
+          <t>159267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>210393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>394731</t>
+          <t>395012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426344</t>
+          <t>426152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323846</t>
+          <t>322759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361414</t>
+          <t>361255</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728201</t>
+          <t>729420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>781983</t>
+          <t>780546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658030</t>
+          <t>654256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>758373</t>
+          <t>752422</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>925052</t>
+          <t>927326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1032607</t>
+          <t>1037900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1621820</t>
+          <t>1612201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1763894</t>
+          <t>1764320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2658728</t>
+          <t>2664679</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2759071</t>
+          <t>2762845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2518518</t>
+          <t>2513225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2626073</t>
+          <t>2623799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5204331</t>
+          <t>5203905</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5346405</t>
+          <t>5356024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118941</t>
+          <t>120463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160105</t>
+          <t>160363</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203431</t>
+          <t>200823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257062</t>
+          <t>254620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331715</t>
+          <t>334595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398519</t>
+          <t>401142</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>592249</t>
+          <t>591991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>633413</t>
+          <t>631891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>734711</t>
+          <t>737153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>788342</t>
+          <t>790950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1345608</t>
+          <t>1342985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1412412</t>
+          <t>1409532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>310734</t>
+          <t>315050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>381825</t>
+          <t>385356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360371</t>
+          <t>361217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>430024</t>
+          <t>429336</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>690766</t>
+          <t>694716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>794046</t>
+          <t>788659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1687813</t>
+          <t>1684282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1758904</t>
+          <t>1754588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1557392</t>
+          <t>1558080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1627045</t>
+          <t>1626199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3263008</t>
+          <t>3268395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3366288</t>
+          <t>3362338</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58683</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93709</t>
+          <t>93465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116811</t>
+          <t>114657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157344</t>
+          <t>156148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184530</t>
+          <t>182649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237516</t>
+          <t>236975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451250</t>
+          <t>451494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>486276</t>
+          <t>485654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>389109</t>
+          <t>390305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>429642</t>
+          <t>431796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853896</t>
+          <t>854437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>906882</t>
+          <t>908763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>515810</t>
+          <t>517225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>604867</t>
+          <t>610953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>714967</t>
+          <t>709898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>809028</t>
+          <t>808456</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1244265</t>
+          <t>1248088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1380486</t>
+          <t>1383636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2762085</t>
+          <t>2755999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2851142</t>
+          <t>2849727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2716613</t>
+          <t>2717185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2810674</t>
+          <t>2815743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5512107</t>
+          <t>5508957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5648328</t>
+          <t>5644505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114537</t>
+          <t>115600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151643</t>
+          <t>154533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>199863</t>
+          <t>200727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238053</t>
+          <t>238325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>325604</t>
+          <t>326866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>379213</t>
+          <t>378685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>363295</t>
+          <t>360405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>400401</t>
+          <t>399338</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>513460</t>
+          <t>513188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551650</t>
+          <t>550786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887238</t>
+          <t>887766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940847</t>
+          <t>939585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290135</t>
+          <t>278180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>469064</t>
+          <t>470983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>477557</t>
+          <t>480976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1092276</t>
+          <t>1041677</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>855756</t>
+          <t>839755</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1657051</t>
+          <t>1561513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1821263</t>
+          <t>1819344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2000192</t>
+          <t>2012147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1141952</t>
+          <t>1192551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1756671</t>
+          <t>1753252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2867504</t>
+          <t>2963042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3668799</t>
+          <t>3684800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116307</t>
+          <t>118497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>163712</t>
+          <t>166598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152124</t>
+          <t>151189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193782</t>
+          <t>193962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280579</t>
+          <t>280047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340807</t>
+          <t>341789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>481158</t>
+          <t>478272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528563</t>
+          <t>526373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465805</t>
+          <t>465625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507463</t>
+          <t>508398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>963651</t>
+          <t>962669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023879</t>
+          <t>1024411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>524994</t>
+          <t>543491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>747921</t>
+          <t>751662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>876989</t>
+          <t>868272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1531163</t>
+          <t>1525198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1510829</t>
+          <t>1509847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2255075</t>
+          <t>2279127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2702215</t>
+          <t>2698474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2925142</t>
+          <t>2906645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2114165</t>
+          <t>2120130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2768339</t>
+          <t>2777056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4840389</t>
+          <t>4816337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5584635</t>
+          <t>5585617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174802</t>
+          <t>174080</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224358</t>
+          <t>224883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>312365</t>
+          <t>309556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>377621</t>
+          <t>376515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>500576</t>
+          <t>497609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>581056</t>
+          <t>582998</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>807365</t>
+          <t>806840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>856921</t>
+          <t>857643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>937492</t>
+          <t>938598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1002748</t>
+          <t>1005557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1765779</t>
+          <t>1763837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1846259</t>
+          <t>1849226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253785</t>
+          <t>255933</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>312891</t>
+          <t>319979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>345939</t>
+          <t>342777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>409083</t>
+          <t>408070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>615404</t>
+          <t>610669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>704252</t>
+          <t>708448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1379637</t>
+          <t>1372549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1438743</t>
+          <t>1436595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1177650</t>
+          <t>1178663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1240794</t>
+          <t>1243956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2575008</t>
+          <t>2570812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2663856</t>
+          <t>2668591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63440</t>
+          <t>63532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99624</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>17,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>106095</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>89246</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>125705</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>26,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>185703</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>161716</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>213751</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>18,07%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>106095</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88194</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>124769</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>26,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>185703</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>159712</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>209597</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451784</t>
+          <t>452663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487968</t>
+          <t>487876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>82,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>370317</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>350707</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>387166</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>77,73%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>73,61%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>842117</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>814069</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>866104</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>81,93%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>370317</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>351643</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>388218</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>77,73%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>73,81%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>81,49%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>842117</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>818223</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>868108</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>81,93%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>515224</t>
+          <t>520496</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>602739</t>
+          <t>605763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>774864</t>
+          <t>772794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>872861</t>
+          <t>869588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1319432</t>
+          <t>1316431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1450792</t>
+          <t>1454107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2672920</t>
+          <t>2669896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2760435</t>
+          <t>2755163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2505396</t>
+          <t>2508669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2603393</t>
+          <t>2605463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5203123</t>
+          <t>5199808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5334483</t>
+          <t>5337484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225645</t>
+          <t>225554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>278109</t>
+          <t>280307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>377691</t>
+          <t>376262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444573</t>
+          <t>445247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616352</t>
+          <t>620000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>706495</t>
+          <t>705800</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>695807</t>
+          <t>693609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748271</t>
+          <t>748362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>892265</t>
+          <t>891591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>959147</t>
+          <t>960576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1604259</t>
+          <t>1604954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1694402</t>
+          <t>1690754</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,17%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>348086</t>
+          <t>350649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>424969</t>
+          <t>423058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>413502</t>
+          <t>416409</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>490932</t>
+          <t>494013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>785830</t>
+          <t>788377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>889402</t>
+          <t>887763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1537034</t>
+          <t>1538945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1613917</t>
+          <t>1611354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1264724</t>
+          <t>1261643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1342154</t>
+          <t>1339247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2828257</t>
+          <t>2829896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2931829</t>
+          <t>2929282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55029</t>
+          <t>54116</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86169</t>
+          <t>86918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97376</t>
+          <t>94797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135872</t>
+          <t>134821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159267</t>
+          <t>158399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>210393</t>
+          <t>208914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>395012</t>
+          <t>394263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426152</t>
+          <t>427065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322759</t>
+          <t>323810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361255</t>
+          <t>363834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>729420</t>
+          <t>730899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>780546</t>
+          <t>781414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>654256</t>
+          <t>655322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>752422</t>
+          <t>757232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>927326</t>
+          <t>924395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1037900</t>
+          <t>1032389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1612201</t>
+          <t>1609897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1764320</t>
+          <t>1759435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2664679</t>
+          <t>2659869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2762845</t>
+          <t>2761779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2513225</t>
+          <t>2518736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2623799</t>
+          <t>2626730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5203905</t>
+          <t>5208790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5356024</t>
+          <t>5358328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120463</t>
+          <t>119539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160363</t>
+          <t>159671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200823</t>
+          <t>200634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>254620</t>
+          <t>252952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>334595</t>
+          <t>330850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401142</t>
+          <t>403226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>591991</t>
+          <t>592683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631891</t>
+          <t>632815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>737153</t>
+          <t>738821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>790950</t>
+          <t>791139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1342985</t>
+          <t>1340901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1409532</t>
+          <t>1413277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>315050</t>
+          <t>309370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>385356</t>
+          <t>378366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>361217</t>
+          <t>358484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>429336</t>
+          <t>431665</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>694716</t>
+          <t>689934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>788659</t>
+          <t>789867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1684282</t>
+          <t>1691272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1754588</t>
+          <t>1760268</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1558080</t>
+          <t>1555751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1626199</t>
+          <t>1628932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3268395</t>
+          <t>3267187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3362338</t>
+          <t>3367120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59305</t>
+          <t>59334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93465</t>
+          <t>93282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114657</t>
+          <t>115793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156148</t>
+          <t>156246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182649</t>
+          <t>184675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236975</t>
+          <t>238330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451494</t>
+          <t>451677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>485654</t>
+          <t>485625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390305</t>
+          <t>390207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431796</t>
+          <t>430660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854437</t>
+          <t>853082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>908763</t>
+          <t>906737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>517225</t>
+          <t>518347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>610953</t>
+          <t>607363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,82 +4983,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>757117</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>713011</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>804454</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>21,47%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>22,82%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1317939</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1250995</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1386374</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>18,15%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>757117</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>709898</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>808456</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,93%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1317939</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1248088</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1383636</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2755999</t>
+          <t>2759589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2849727</t>
+          <t>2848605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,82 +5096,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>81,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2768524</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2721187</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2812630</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>78,53%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>77,18%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>5574654</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>5506219</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5641598</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>79,89%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>81,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2768524</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2717185</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2815743</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>78,53%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>77,07%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>79,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5296</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>5574654</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>5508957</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5644505</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>80,88%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>79,93%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>81,89%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>132945</t>
+          <t>141516</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115600</t>
+          <t>122359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154533</t>
+          <t>164179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>218968</t>
+          <t>239669</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>200727</t>
+          <t>219841</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238325</t>
+          <t>258864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>381185</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>326866</t>
+          <t>353867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>378685</t>
+          <t>408330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>381993</t>
+          <t>437013</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360405</t>
+          <t>414350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399338</t>
+          <t>456170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>532545</t>
+          <t>579821</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>513188</t>
+          <t>560626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550786</t>
+          <t>599649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>914538</t>
+          <t>1016835</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>887766</t>
+          <t>989690</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939585</t>
+          <t>1044153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751513</t>
+          <t>819490</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751513</t>
+          <t>819490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751513</t>
+          <t>819490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266451</t>
+          <t>1398020</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266451</t>
+          <t>1398020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266451</t>
+          <t>1398020</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>403857</t>
+          <t>431483</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278180</t>
+          <t>388331</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>470983</t>
+          <t>472829</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>654950</t>
+          <t>503018</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>480976</t>
+          <t>469888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1041677</t>
+          <t>542040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1058807</t>
+          <t>934501</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>839755</t>
+          <t>876545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1561513</t>
+          <t>990043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1886470</t>
+          <t>1799083</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1819344</t>
+          <t>1757737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2012147</t>
+          <t>1842235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1579278</t>
+          <t>1664710</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1192551</t>
+          <t>1625688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1753252</t>
+          <t>1697840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3465748</t>
+          <t>3463793</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2963042</t>
+          <t>3408251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3684800</t>
+          <t>3521749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,07%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234228</t>
+          <t>2167728</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234228</t>
+          <t>2167728</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234228</t>
+          <t>2167728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524555</t>
+          <t>4398294</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524555</t>
+          <t>4398294</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524555</t>
+          <t>4398294</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>139419</t>
+          <t>159315</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118497</t>
+          <t>135400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166598</t>
+          <t>186032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>190096</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151189</t>
+          <t>168638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193962</t>
+          <t>213439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>310596</t>
+          <t>349411</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280047</t>
+          <t>318359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>341789</t>
+          <t>386680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>505451</t>
+          <t>550302</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>478272</t>
+          <t>523585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526373</t>
+          <t>574217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>488411</t>
+          <t>543909</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>465625</t>
+          <t>520566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>508398</t>
+          <t>565367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>993862</t>
+          <t>1094210</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>962669</t>
+          <t>1056941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1024411</t>
+          <t>1125262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>709617</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>709617</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644870</t>
+          <t>709617</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659587</t>
+          <t>734005</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304458</t>
+          <t>1443621</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304458</t>
+          <t>1443621</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304458</t>
+          <t>1443621</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>676222</t>
+          <t>732314</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>543491</t>
+          <t>683276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>751662</t>
+          <t>787739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1045094</t>
+          <t>932783</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>868272</t>
+          <t>884906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1525198</t>
+          <t>981207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1721316</t>
+          <t>1665098</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1509847</t>
+          <t>1596237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2279127</t>
+          <t>1735347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2773914</t>
+          <t>2786398</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2698474</t>
+          <t>2730973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2906645</t>
+          <t>2835436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2600234</t>
+          <t>2788439</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2120130</t>
+          <t>2740015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2777056</t>
+          <t>2836316</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5374148</t>
+          <t>5574837</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4816337</t>
+          <t>5504588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5585617</t>
+          <t>5643698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450136</t>
+          <t>3518712</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450136</t>
+          <t>3518712</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450136</t>
+          <t>3518712</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3645328</t>
+          <t>3721222</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3645328</t>
+          <t>3721222</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3645328</t>
+          <t>3721222</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095464</t>
+          <t>7239935</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095464</t>
+          <t>7239935</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095464</t>
+          <t>7239935</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
